--- a/LubanTmpl/Datas/__tables__.xlsx
+++ b/LubanTmpl/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30313"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49F87AC-18E4-49B5-90BE-8879F5F94FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15973FFA-272C-456F-8A55-929E56970B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27210" yWindow="1620" windowWidth="28830" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="0" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -101,10 +101,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>UIParam</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbUIParam</t>
@@ -139,12 +135,27 @@
     <t>audio.xlsx</t>
   </si>
   <si>
-    <t>Audio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TbAudio</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbApp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AppCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AudioCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIParamCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>app.xlsx</t>
   </si>
 </sst>
 </file>
@@ -508,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -610,30 +621,44 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/LubanTmpl/Datas/__tables__.xlsx
+++ b/LubanTmpl/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15973FFA-272C-456F-8A55-929E56970B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73ED559F-889B-4237-B817-2CDD4402C0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="0" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,17 @@
   </si>
   <si>
     <t>app.xlsx</t>
+  </si>
+  <si>
+    <t>localization.xlsx</t>
+  </si>
+  <si>
+    <t>TbLocalization</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LocalizationCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -519,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -661,6 +672,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LubanTmpl/Datas/__tables__.xlsx
+++ b/LubanTmpl/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73ED559F-889B-4237-B817-2CDD4402C0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854CA0C4-998B-444A-8E18-A26E4ADA46B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="0" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="570" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -166,6 +166,32 @@
   </si>
   <si>
     <t>LocalizationCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>prop.xlsx</t>
+  </si>
+  <si>
+    <t>PropCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbProp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>param.xlsx</t>
+  </si>
+  <si>
+    <t>TbParam</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamCfg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -530,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -686,6 +712,37 @@
         <v>36</v>
       </c>
     </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
